--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SCRIPT PDFS\PDF CALIDAD\IPS SIN AUTORIZACIONES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN AUTORIZACIONES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374151C6-9325-47E4-8EA4-BFE6FAF5816E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CA787D-50E6-4092-B479-2187152E8712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -56,19 +56,19 @@
     <t>campoe</t>
   </si>
   <si>
-    <t>0094-2024</t>
-  </si>
-  <si>
-    <t>FUNDACION SOCIAL SOMOS CONSTRUCTORES DE VIDA - COVIDA</t>
-  </si>
-  <si>
-    <t>20.02.2026</t>
-  </si>
-  <si>
     <t>ENERO</t>
   </si>
   <si>
-    <t>ENERO 2026</t>
+    <t>20.03.2026</t>
+  </si>
+  <si>
+    <t>ENERO - FEBRERO 2026</t>
+  </si>
+  <si>
+    <t>0734-2025</t>
+  </si>
+  <si>
+    <t>SANAR CLINICA DE HERIDAS S.A.S</t>
   </si>
 </sst>
 </file>
@@ -479,25 +479,26 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E2" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN AUTORIZACIONES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CA787D-50E6-4092-B479-2187152E8712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEB8D35-DAD5-45DD-8222-2A79C7370CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>campoa</t>
   </si>
@@ -53,22 +53,46 @@
     <t>campod</t>
   </si>
   <si>
-    <t>campoe</t>
-  </si>
-  <si>
-    <t>ENERO</t>
-  </si>
-  <si>
-    <t>20.03.2026</t>
-  </si>
-  <si>
-    <t>ENERO - FEBRERO 2026</t>
-  </si>
-  <si>
-    <t>0734-2025</t>
-  </si>
-  <si>
-    <t>SANAR CLINICA DE HERIDAS S.A.S</t>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>ERIKA JOHANNA PULIDO DURAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO RAMON MOJICA RODRIGUEZ - ORTOPEDIA Y TRAUMATOLOGIA </t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SAN VICENTE DE RAMIRIQUÍ</t>
+  </si>
+  <si>
+    <t>FUNDACIÓN JAVERIANA DE SERVICIOS MEDICO ODONTOLÓGICOS INTERUNIVERSITARIOS CARLOS MARQUEZ VILLEGAS</t>
+  </si>
+  <si>
+    <t>REHINTEGRAR LIMITADA</t>
+  </si>
+  <si>
+    <t>ELECTROFISIATRIA SAS</t>
+  </si>
+  <si>
+    <t>0171-2026</t>
+  </si>
+  <si>
+    <t>0713-2024</t>
+  </si>
+  <si>
+    <t>0916-2021</t>
+  </si>
+  <si>
+    <t>0863-2025</t>
+  </si>
+  <si>
+    <t>0838-2024</t>
+  </si>
+  <si>
+    <t>0565-2024</t>
+  </si>
+  <si>
+    <t>ENERO A MARZO 2026</t>
   </si>
 </sst>
 </file>
@@ -452,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -462,7 +486,7 @@
     <col min="5" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -475,29 +499,93 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="180" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}"/>
+  <autoFilter ref="A1:D1" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN AUTORIZACIONES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEB8D35-DAD5-45DD-8222-2A79C7370CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378DC138-0562-42AF-8D90-9537EFB6EA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>campoa</t>
   </si>
@@ -53,18 +53,12 @@
     <t>campod</t>
   </si>
   <si>
-    <t>20.04.2026</t>
-  </si>
-  <si>
     <t>ERIKA JOHANNA PULIDO DURAN</t>
   </si>
   <si>
     <t xml:space="preserve">DIEGO RAMON MOJICA RODRIGUEZ - ORTOPEDIA Y TRAUMATOLOGIA </t>
   </si>
   <si>
-    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SAN VICENTE DE RAMIRIQUÍ</t>
-  </si>
-  <si>
     <t>FUNDACIÓN JAVERIANA DE SERVICIOS MEDICO ODONTOLÓGICOS INTERUNIVERSITARIOS CARLOS MARQUEZ VILLEGAS</t>
   </si>
   <si>
@@ -80,9 +74,6 @@
     <t>0713-2024</t>
   </si>
   <si>
-    <t>0916-2021</t>
-  </si>
-  <si>
     <t>0863-2025</t>
   </si>
   <si>
@@ -92,7 +83,10 @@
     <t>0565-2024</t>
   </si>
   <si>
-    <t>ENERO A MARZO 2026</t>
+    <t>13.04.2026</t>
+  </si>
+  <si>
+    <t>I TRIMESTRE</t>
   </si>
 </sst>
 </file>
@@ -500,89 +494,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}"/>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN AUTORIZACIONES/indicadores sin autorizaciones 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN AUTORIZACIONES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378DC138-0562-42AF-8D90-9537EFB6EA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710C03AA-D135-4B9E-8AE2-6282547D9E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,10 @@
     <t>0565-2024</t>
   </si>
   <si>
-    <t>13.04.2026</t>
-  </si>
-  <si>
     <t>I TRIMESTRE</t>
+  </si>
+  <si>
+    <t>20.04.2026</t>
   </si>
 </sst>
 </file>
@@ -496,10 +496,10 @@
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -510,10 +510,10 @@
     </row>
     <row r="3" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
@@ -538,10 +538,10 @@
     </row>
     <row r="5" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -552,10 +552,10 @@
     </row>
     <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
